--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121130879</v>
       </c>
       <c r="B2" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121131364</v>
+        <v>121131447</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581181</v>
+        <v>581070</v>
       </c>
       <c r="R3" t="n">
-        <v>7053019</v>
+        <v>7053041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +902,7 @@
         <v>121130108</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121131447</v>
+        <v>121131364</v>
       </c>
       <c r="B5" t="n">
-        <v>90973</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1023,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581070</v>
+        <v>581181</v>
       </c>
       <c r="R5" t="n">
-        <v>7053041</v>
+        <v>7053019</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121131447</v>
+        <v>121131364</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581070</v>
+        <v>581181</v>
       </c>
       <c r="R3" t="n">
-        <v>7053041</v>
+        <v>7053019</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121130108</v>
+        <v>121131447</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581052</v>
+        <v>581070</v>
       </c>
       <c r="R4" t="n">
-        <v>7053002</v>
+        <v>7053041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121131364</v>
+        <v>121130108</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,42 +1027,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581181</v>
+        <v>581052</v>
       </c>
       <c r="R5" t="n">
-        <v>7053019</v>
+        <v>7053002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121130879</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121131364</v>
+        <v>121131447</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>90995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581181</v>
+        <v>581070</v>
       </c>
       <c r="R3" t="n">
-        <v>7053019</v>
+        <v>7053041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121131447</v>
+        <v>121131364</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581070</v>
+        <v>581181</v>
       </c>
       <c r="R4" t="n">
-        <v>7053041</v>
+        <v>7053019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1018,7 @@
         <v>121130108</v>
       </c>
       <c r="B5" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121130879</v>
+        <v>121130108</v>
       </c>
       <c r="B2" t="n">
         <v>79685</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581211</v>
+        <v>581052</v>
       </c>
       <c r="R2" t="n">
-        <v>7053043</v>
+        <v>7053002</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121131447</v>
+        <v>121131364</v>
       </c>
       <c r="B3" t="n">
-        <v>90995</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581070</v>
+        <v>581181</v>
       </c>
       <c r="R3" t="n">
-        <v>7053041</v>
+        <v>7053019</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121131364</v>
+        <v>121130879</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581181</v>
+        <v>581211</v>
       </c>
       <c r="R4" t="n">
-        <v>7053019</v>
+        <v>7053043</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121130108</v>
+        <v>121131447</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>90996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581052</v>
+        <v>581070</v>
       </c>
       <c r="R5" t="n">
-        <v>7053002</v>
+        <v>7053041</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121130108</v>
+        <v>121130879</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581052</v>
+        <v>581211</v>
       </c>
       <c r="R2" t="n">
-        <v>7053002</v>
+        <v>7053043</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121131364</v>
+        <v>121130108</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581181</v>
+        <v>581052</v>
       </c>
       <c r="R3" t="n">
-        <v>7053019</v>
+        <v>7053002</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121130879</v>
+        <v>121131447</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>90999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581211</v>
+        <v>581070</v>
       </c>
       <c r="R4" t="n">
-        <v>7053043</v>
+        <v>7053041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121131447</v>
+        <v>121131364</v>
       </c>
       <c r="B5" t="n">
-        <v>90996</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1023,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581070</v>
+        <v>581181</v>
       </c>
       <c r="R5" t="n">
-        <v>7053041</v>
+        <v>7053019</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121130879</v>
+        <v>121131364</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581211</v>
+        <v>581181</v>
       </c>
       <c r="R2" t="n">
-        <v>7053043</v>
+        <v>7053019</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121130108</v>
+        <v>121131447</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>90999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581052</v>
+        <v>581070</v>
       </c>
       <c r="R3" t="n">
-        <v>7053002</v>
+        <v>7053041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121131447</v>
+        <v>121130108</v>
       </c>
       <c r="B4" t="n">
-        <v>90999</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581070</v>
+        <v>581052</v>
       </c>
       <c r="R4" t="n">
-        <v>7053041</v>
+        <v>7053002</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121131364</v>
+        <v>121130879</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,42 +1027,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581181</v>
+        <v>581211</v>
       </c>
       <c r="R5" t="n">
-        <v>7053019</v>
+        <v>7053043</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124299212</v>
+        <v>124302071</v>
       </c>
       <c r="B6" t="n">
         <v>91012</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581119</v>
+        <v>581211</v>
       </c>
       <c r="R6" t="n">
-        <v>7053034</v>
+        <v>7053014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124302071</v>
+        <v>124300269</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581211</v>
+        <v>581175</v>
       </c>
       <c r="R7" t="n">
-        <v>7053014</v>
+        <v>7053047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,22 +1339,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124302493</v>
+        <v>124303683</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,38 +1363,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581190</v>
+        <v>581075</v>
       </c>
       <c r="R8" t="n">
-        <v>7053006</v>
+        <v>7053018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1441,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124299626</v>
+        <v>124299905</v>
       </c>
       <c r="B9" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,34 +1489,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581134</v>
+        <v>581157</v>
       </c>
       <c r="R9" t="n">
-        <v>7053050</v>
+        <v>7053041</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,22 +1577,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124298991</v>
+        <v>124299212</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,42 +1601,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581099</v>
+        <v>581119</v>
       </c>
       <c r="R10" t="n">
-        <v>7053032</v>
+        <v>7053034</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299905</v>
+        <v>124300324</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,42 +1713,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581157</v>
+        <v>581191</v>
       </c>
       <c r="R11" t="n">
-        <v>7053041</v>
+        <v>7053034</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,22 +1801,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124302024</v>
+        <v>124302148</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,38 +1825,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581189</v>
+        <v>581210</v>
       </c>
       <c r="R12" t="n">
-        <v>7052999</v>
+        <v>7053013</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124303683</v>
+        <v>124303915</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,39 +1945,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581075</v>
+        <v>581062</v>
       </c>
       <c r="R13" t="n">
-        <v>7053018</v>
+        <v>7053037</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2009,12 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124303795</v>
+        <v>124302493</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,25 +2053,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581080</v>
+        <v>581190</v>
       </c>
       <c r="R14" t="n">
-        <v>7053021</v>
+        <v>7053006</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124300269</v>
+        <v>124298991</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,38 +2165,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581175</v>
+        <v>581099</v>
       </c>
       <c r="R15" t="n">
-        <v>7053047</v>
+        <v>7053032</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,22 +2257,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124302148</v>
+        <v>124302024</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,42 +2281,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581210</v>
+        <v>581189</v>
       </c>
       <c r="R16" t="n">
-        <v>7053013</v>
+        <v>7052999</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124302441</v>
+        <v>124303795</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,43 +2393,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581183</v>
+        <v>581080</v>
       </c>
       <c r="R17" t="n">
-        <v>7052996</v>
+        <v>7053021</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124302611</v>
+        <v>124299626</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>91673</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,43 +2505,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>898</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581184</v>
+        <v>581134</v>
       </c>
       <c r="R18" t="n">
-        <v>7053000</v>
+        <v>7053050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2588,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,22 +2593,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124303915</v>
+        <v>124302611</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,38 +2617,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581062</v>
+        <v>581184</v>
       </c>
       <c r="R19" t="n">
-        <v>7053037</v>
+        <v>7053000</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2695,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,22 +2710,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124300324</v>
+        <v>124302441</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2739,38 +2734,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581191</v>
+        <v>581183</v>
       </c>
       <c r="R20" t="n">
-        <v>7053034</v>
+        <v>7052996</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,12 +2827,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124302071</v>
+        <v>124302493</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1139,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581211</v>
+        <v>581190</v>
       </c>
       <c r="R6" t="n">
-        <v>7053014</v>
+        <v>7053006</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124300269</v>
+        <v>124299905</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,38 +1251,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581175</v>
+        <v>581157</v>
       </c>
       <c r="R7" t="n">
-        <v>7053047</v>
+        <v>7053041</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,22 +1343,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124303683</v>
+        <v>124302441</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,31 +1367,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1396,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581075</v>
+        <v>581183</v>
       </c>
       <c r="R8" t="n">
-        <v>7053018</v>
+        <v>7052996</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,12 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124299905</v>
+        <v>124302611</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,30 +1484,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581157</v>
+        <v>581184</v>
       </c>
       <c r="R9" t="n">
-        <v>7053041</v>
+        <v>7053000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,22 +1577,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124299212</v>
+        <v>124298991</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,38 +1601,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581119</v>
+        <v>581099</v>
       </c>
       <c r="R10" t="n">
-        <v>7053034</v>
+        <v>7053032</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124300324</v>
+        <v>124300269</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,21 +1721,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,10 +1745,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581191</v>
+        <v>581175</v>
       </c>
       <c r="R11" t="n">
-        <v>7053034</v>
+        <v>7053047</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1813,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124302148</v>
+        <v>124300324</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,42 +1829,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581210</v>
+        <v>581191</v>
       </c>
       <c r="R12" t="n">
-        <v>7053013</v>
+        <v>7053034</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,22 +1917,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124303915</v>
+        <v>124303795</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581062</v>
+        <v>581080</v>
       </c>
       <c r="R13" t="n">
-        <v>7053037</v>
+        <v>7053021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124302493</v>
+        <v>124303683</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,38 +2053,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581190</v>
+        <v>581075</v>
       </c>
       <c r="R14" t="n">
-        <v>7053006</v>
+        <v>7053018</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2131,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124298991</v>
+        <v>124302071</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,42 +2175,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581099</v>
+        <v>581211</v>
       </c>
       <c r="R15" t="n">
-        <v>7053032</v>
+        <v>7053014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2248,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,7 +2275,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124302024</v>
+        <v>124303915</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2309,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581189</v>
+        <v>581062</v>
       </c>
       <c r="R16" t="n">
-        <v>7052999</v>
+        <v>7053037</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2350,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2360,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124303795</v>
+        <v>124299626</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,25 +2399,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2421,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581080</v>
+        <v>581134</v>
       </c>
       <c r="R17" t="n">
-        <v>7053021</v>
+        <v>7053050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,7 +2462,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2466,7 +2472,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,22 +2487,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124299626</v>
+        <v>124302024</v>
       </c>
       <c r="B18" t="n">
-        <v>91673</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,25 +2511,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2533,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581134</v>
+        <v>581189</v>
       </c>
       <c r="R18" t="n">
-        <v>7053050</v>
+        <v>7052999</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2578,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,22 +2599,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124302611</v>
+        <v>124299212</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,43 +2623,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581184</v>
+        <v>581119</v>
       </c>
       <c r="R19" t="n">
-        <v>7053000</v>
+        <v>7053034</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2685,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,7 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,22 +2711,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124302441</v>
+        <v>124302148</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,31 +2735,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581183</v>
+        <v>581210</v>
       </c>
       <c r="R20" t="n">
-        <v>7052996</v>
+        <v>7053013</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124302493</v>
+        <v>124302071</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1139,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581190</v>
+        <v>581211</v>
       </c>
       <c r="R6" t="n">
-        <v>7053006</v>
+        <v>7053014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124299905</v>
+        <v>124302024</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,42 +1251,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581157</v>
+        <v>581189</v>
       </c>
       <c r="R7" t="n">
-        <v>7053041</v>
+        <v>7052999</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124302441</v>
+        <v>124299626</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>91673</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,43 +1363,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>898</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581183</v>
+        <v>581134</v>
       </c>
       <c r="R8" t="n">
-        <v>7052996</v>
+        <v>7053050</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,22 +1451,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124302611</v>
+        <v>124303683</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,31 +1475,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1517,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581184</v>
+        <v>581075</v>
       </c>
       <c r="R9" t="n">
-        <v>7053000</v>
+        <v>7053018</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1553,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,22 +1573,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124298991</v>
+        <v>124303795</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,42 +1597,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581099</v>
+        <v>581080</v>
       </c>
       <c r="R10" t="n">
-        <v>7053032</v>
+        <v>7053021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124300269</v>
+        <v>124299905</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,38 +1709,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581175</v>
+        <v>581157</v>
       </c>
       <c r="R11" t="n">
-        <v>7053047</v>
+        <v>7053041</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,22 +1801,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124300324</v>
+        <v>124298991</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,38 +1825,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581191</v>
+        <v>581099</v>
       </c>
       <c r="R12" t="n">
-        <v>7053034</v>
+        <v>7053032</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,22 +1917,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124303795</v>
+        <v>124302441</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,38 +1941,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581080</v>
+        <v>581183</v>
       </c>
       <c r="R13" t="n">
-        <v>7053021</v>
+        <v>7052996</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124303683</v>
+        <v>124302493</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,43 +2058,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581075</v>
+        <v>581190</v>
       </c>
       <c r="R14" t="n">
-        <v>7053018</v>
+        <v>7053006</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,12 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124302071</v>
+        <v>124300269</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2174,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581211</v>
+        <v>581175</v>
       </c>
       <c r="R15" t="n">
-        <v>7053014</v>
+        <v>7053047</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,19 +2258,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124303915</v>
+        <v>124300324</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581062</v>
+        <v>581191</v>
       </c>
       <c r="R16" t="n">
-        <v>7053037</v>
+        <v>7053034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,7 +2345,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2360,7 +2355,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,22 +2370,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124299626</v>
+        <v>124299212</v>
       </c>
       <c r="B17" t="n">
-        <v>91673</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,25 +2394,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2427,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581134</v>
+        <v>581119</v>
       </c>
       <c r="R17" t="n">
-        <v>7053050</v>
+        <v>7053034</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2462,7 +2457,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2472,7 +2467,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,22 +2482,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124302024</v>
+        <v>124302611</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,38 +2506,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581189</v>
+        <v>581184</v>
       </c>
       <c r="R18" t="n">
-        <v>7052999</v>
+        <v>7053000</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,22 +2599,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124299212</v>
+        <v>124303915</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581119</v>
+        <v>581062</v>
       </c>
       <c r="R19" t="n">
-        <v>7053034</v>
+        <v>7053037</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124302071</v>
+        <v>124303915</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581211</v>
+        <v>581062</v>
       </c>
       <c r="R6" t="n">
-        <v>7053014</v>
+        <v>7053037</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124302024</v>
+        <v>124300324</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581189</v>
+        <v>581191</v>
       </c>
       <c r="R7" t="n">
-        <v>7052999</v>
+        <v>7053034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,22 +1339,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124299626</v>
+        <v>124302148</v>
       </c>
       <c r="B8" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,34 +1367,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581134</v>
+        <v>581210</v>
       </c>
       <c r="R8" t="n">
-        <v>7053050</v>
+        <v>7053013</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,22 +1455,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124303683</v>
+        <v>124299212</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,39 +1483,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581075</v>
+        <v>581119</v>
       </c>
       <c r="R9" t="n">
-        <v>7053018</v>
+        <v>7053034</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,12 +1552,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124303795</v>
+        <v>124302611</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,38 +1591,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581080</v>
+        <v>581184</v>
       </c>
       <c r="R10" t="n">
-        <v>7053021</v>
+        <v>7053000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,22 +1684,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299905</v>
+        <v>124299626</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91673</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,38 +1712,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581157</v>
+        <v>581134</v>
       </c>
       <c r="R11" t="n">
-        <v>7053041</v>
+        <v>7053050</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124298991</v>
+        <v>124303683</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,30 +1820,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1857,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581099</v>
+        <v>581075</v>
       </c>
       <c r="R12" t="n">
-        <v>7053032</v>
+        <v>7053018</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1898,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124302441</v>
+        <v>124302493</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,39 +1946,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581183</v>
+        <v>581190</v>
       </c>
       <c r="R13" t="n">
-        <v>7052996</v>
+        <v>7053006</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124302493</v>
+        <v>124300269</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,25 +2054,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +2082,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581190</v>
+        <v>581175</v>
       </c>
       <c r="R14" t="n">
-        <v>7053006</v>
+        <v>7053047</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,22 +2142,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124300269</v>
+        <v>124302441</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,38 +2166,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581175</v>
+        <v>581183</v>
       </c>
       <c r="R15" t="n">
-        <v>7053047</v>
+        <v>7052996</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,22 +2259,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124300324</v>
+        <v>124303795</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,21 +2287,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2310,10 +2311,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581191</v>
+        <v>581080</v>
       </c>
       <c r="R16" t="n">
-        <v>7053034</v>
+        <v>7053021</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2355,7 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,19 +2371,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124299212</v>
+        <v>124302071</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2422,10 +2423,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581119</v>
+        <v>581211</v>
       </c>
       <c r="R17" t="n">
-        <v>7053034</v>
+        <v>7053014</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2467,7 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124302611</v>
+        <v>124299905</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2506,31 +2507,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581184</v>
+        <v>581157</v>
       </c>
       <c r="R18" t="n">
-        <v>7053000</v>
+        <v>7053041</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,19 +2599,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124303915</v>
+        <v>124302024</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581062</v>
+        <v>581189</v>
       </c>
       <c r="R19" t="n">
-        <v>7053037</v>
+        <v>7052999</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2723,7 +2723,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124302148</v>
+        <v>124298991</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581210</v>
+        <v>581099</v>
       </c>
       <c r="R20" t="n">
-        <v>7053013</v>
+        <v>7053032</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124303915</v>
+        <v>124300269</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581062</v>
+        <v>581175</v>
       </c>
       <c r="R6" t="n">
-        <v>7053037</v>
+        <v>7053047</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124300324</v>
+        <v>124302441</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,38 +1251,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581191</v>
+        <v>581183</v>
       </c>
       <c r="R7" t="n">
-        <v>7053034</v>
+        <v>7052996</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,22 +1344,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124302148</v>
+        <v>124303915</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,42 +1368,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581210</v>
+        <v>581062</v>
       </c>
       <c r="R8" t="n">
-        <v>7053013</v>
+        <v>7053037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124299212</v>
+        <v>124300324</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,7 +1508,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581119</v>
+        <v>581191</v>
       </c>
       <c r="R9" t="n">
         <v>7053034</v>
@@ -1542,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,22 +1568,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124302611</v>
+        <v>124302024</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,43 +1592,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581184</v>
+        <v>581189</v>
       </c>
       <c r="R10" t="n">
-        <v>7053000</v>
+        <v>7052999</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,22 +1680,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299626</v>
+        <v>124302148</v>
       </c>
       <c r="B11" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,34 +1708,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581134</v>
+        <v>581210</v>
       </c>
       <c r="R11" t="n">
-        <v>7053050</v>
+        <v>7053013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124303683</v>
+        <v>124302611</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,31 +1820,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581075</v>
+        <v>581184</v>
       </c>
       <c r="R12" t="n">
-        <v>7053018</v>
+        <v>7053000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,12 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,22 +1913,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124302493</v>
+        <v>124299905</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,38 +1937,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581190</v>
+        <v>581157</v>
       </c>
       <c r="R13" t="n">
-        <v>7053006</v>
+        <v>7053041</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124300269</v>
+        <v>124298991</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,38 +2053,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581175</v>
+        <v>581099</v>
       </c>
       <c r="R14" t="n">
-        <v>7053047</v>
+        <v>7053032</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,22 +2145,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124302441</v>
+        <v>124299626</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>91673</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,43 +2169,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>898</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581183</v>
+        <v>581134</v>
       </c>
       <c r="R15" t="n">
-        <v>7052996</v>
+        <v>7053050</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,19 +2257,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124303795</v>
+        <v>124302071</v>
       </c>
       <c r="B16" t="n">
         <v>91012</v>
@@ -2311,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581080</v>
+        <v>581211</v>
       </c>
       <c r="R16" t="n">
-        <v>7053021</v>
+        <v>7053014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2354,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124302071</v>
+        <v>124303683</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,34 +2397,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581211</v>
+        <v>581075</v>
       </c>
       <c r="R17" t="n">
-        <v>7053014</v>
+        <v>7053018</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2468,7 +2471,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,10 +2503,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124299905</v>
+        <v>124299212</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,42 +2515,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581157</v>
+        <v>581119</v>
       </c>
       <c r="R18" t="n">
-        <v>7053041</v>
+        <v>7053034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,7 +2578,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2588,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,10 +2615,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124302024</v>
+        <v>124302493</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2623,25 +2627,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2651,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581189</v>
+        <v>581190</v>
       </c>
       <c r="R19" t="n">
-        <v>7052999</v>
+        <v>7053006</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2686,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2723,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124298991</v>
+        <v>124303795</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2735,42 +2739,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581099</v>
+        <v>581080</v>
       </c>
       <c r="R20" t="n">
-        <v>7053032</v>
+        <v>7053021</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124298991</v>
+        <v>124299626</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91673</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,38 +2057,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581099</v>
+        <v>581134</v>
       </c>
       <c r="R14" t="n">
-        <v>7053032</v>
+        <v>7053050</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,22 +2141,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124299626</v>
+        <v>124298991</v>
       </c>
       <c r="B15" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,34 +2169,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581134</v>
+        <v>581099</v>
       </c>
       <c r="R15" t="n">
-        <v>7053050</v>
+        <v>7053032</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,12 +2257,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124300269</v>
+        <v>124302071</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581175</v>
+        <v>581211</v>
       </c>
       <c r="R6" t="n">
-        <v>7053047</v>
+        <v>7053014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124302441</v>
+        <v>124299905</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,31 +1251,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581183</v>
+        <v>581157</v>
       </c>
       <c r="R7" t="n">
-        <v>7052996</v>
+        <v>7053041</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124303915</v>
+        <v>124302441</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,38 +1367,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581062</v>
+        <v>581183</v>
       </c>
       <c r="R8" t="n">
-        <v>7053037</v>
+        <v>7052996</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124300324</v>
+        <v>124298991</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,38 +1484,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581191</v>
+        <v>581099</v>
       </c>
       <c r="R9" t="n">
-        <v>7053034</v>
+        <v>7053032</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,19 +1576,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124302024</v>
+        <v>124300324</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1620,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581189</v>
+        <v>581191</v>
       </c>
       <c r="R10" t="n">
-        <v>7052999</v>
+        <v>7053034</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1673,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,12 +1688,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1808,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124302611</v>
+        <v>124300269</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,43 +1828,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581184</v>
+        <v>581175</v>
       </c>
       <c r="R12" t="n">
-        <v>7053000</v>
+        <v>7053047</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124299905</v>
+        <v>124302024</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,42 +1940,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581157</v>
+        <v>581189</v>
       </c>
       <c r="R13" t="n">
-        <v>7053041</v>
+        <v>7052999</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2013,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124299626</v>
+        <v>124302611</v>
       </c>
       <c r="B14" t="n">
-        <v>91673</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,38 +2052,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>898</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581134</v>
+        <v>581184</v>
       </c>
       <c r="R14" t="n">
-        <v>7053050</v>
+        <v>7053000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,22 +2145,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124298991</v>
+        <v>124303915</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,42 +2169,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581099</v>
+        <v>581062</v>
       </c>
       <c r="R15" t="n">
-        <v>7053032</v>
+        <v>7053037</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,7 +2269,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124302071</v>
+        <v>124299212</v>
       </c>
       <c r="B16" t="n">
         <v>91012</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581211</v>
+        <v>581119</v>
       </c>
       <c r="R16" t="n">
-        <v>7053014</v>
+        <v>7053034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124303683</v>
+        <v>124303795</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,39 +2397,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581075</v>
+        <v>581080</v>
       </c>
       <c r="R17" t="n">
-        <v>7053018</v>
+        <v>7053021</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,12 +2466,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,10 +2493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124299212</v>
+        <v>124302493</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,25 +2505,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2543,10 +2533,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581119</v>
+        <v>581190</v>
       </c>
       <c r="R18" t="n">
-        <v>7053034</v>
+        <v>7053006</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2588,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2615,10 +2605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124302493</v>
+        <v>124299626</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>91673</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,25 +2617,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2645,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581190</v>
+        <v>581134</v>
       </c>
       <c r="R19" t="n">
-        <v>7053006</v>
+        <v>7053050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,7 +2680,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2690,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,22 +2705,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124303795</v>
+        <v>124303683</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2743,34 +2733,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581080</v>
+        <v>581075</v>
       </c>
       <c r="R20" t="n">
-        <v>7053021</v>
+        <v>7053018</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2807,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124302071</v>
+        <v>124299212</v>
       </c>
       <c r="B6" t="n">
         <v>91012</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581211</v>
+        <v>581119</v>
       </c>
       <c r="R6" t="n">
-        <v>7053014</v>
+        <v>7053034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124299905</v>
+        <v>124303683</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,30 +1251,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1283,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581157</v>
+        <v>581075</v>
       </c>
       <c r="R7" t="n">
-        <v>7053041</v>
+        <v>7053018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124302441</v>
+        <v>124299905</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,31 +1373,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1400,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581183</v>
+        <v>581157</v>
       </c>
       <c r="R8" t="n">
-        <v>7052996</v>
+        <v>7053041</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124298991</v>
+        <v>124302024</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,42 +1489,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581099</v>
+        <v>581189</v>
       </c>
       <c r="R9" t="n">
-        <v>7053032</v>
+        <v>7052999</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,7 +1589,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124300324</v>
+        <v>124303915</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1628,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581191</v>
+        <v>581062</v>
       </c>
       <c r="R10" t="n">
-        <v>7053034</v>
+        <v>7053037</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,22 +1689,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124302148</v>
+        <v>124302493</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,42 +1713,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581210</v>
+        <v>581190</v>
       </c>
       <c r="R11" t="n">
-        <v>7053013</v>
+        <v>7053006</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124300269</v>
+        <v>124302611</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,38 +1825,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581175</v>
+        <v>581184</v>
       </c>
       <c r="R12" t="n">
-        <v>7053047</v>
+        <v>7053000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124302024</v>
+        <v>124303795</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,21 +1946,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1968,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581189</v>
+        <v>581080</v>
       </c>
       <c r="R13" t="n">
-        <v>7052999</v>
+        <v>7053021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124302611</v>
+        <v>124302148</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2052,31 +2054,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2085,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581184</v>
+        <v>581210</v>
       </c>
       <c r="R14" t="n">
-        <v>7053000</v>
+        <v>7053013</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,22 +2146,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124303915</v>
+        <v>124302071</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,21 +2174,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2197,10 +2198,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581062</v>
+        <v>581211</v>
       </c>
       <c r="R15" t="n">
-        <v>7053037</v>
+        <v>7053014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124299212</v>
+        <v>124300324</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,21 +2286,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,7 +2310,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581119</v>
+        <v>581191</v>
       </c>
       <c r="R16" t="n">
         <v>7053034</v>
@@ -2344,7 +2345,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2355,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,22 +2370,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124303795</v>
+        <v>124299626</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,25 +2394,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2421,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581080</v>
+        <v>581134</v>
       </c>
       <c r="R17" t="n">
-        <v>7053021</v>
+        <v>7053050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,7 +2457,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2466,7 +2467,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,22 +2482,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124302493</v>
+        <v>124298991</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,38 +2506,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581190</v>
+        <v>581099</v>
       </c>
       <c r="R18" t="n">
-        <v>7053006</v>
+        <v>7053032</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2578,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2605,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124299626</v>
+        <v>124300269</v>
       </c>
       <c r="B19" t="n">
-        <v>91673</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,25 +2622,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2645,10 +2650,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581134</v>
+        <v>581175</v>
       </c>
       <c r="R19" t="n">
-        <v>7053050</v>
+        <v>7053047</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2680,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2690,7 +2695,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,22 +2710,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124303683</v>
+        <v>124302441</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,31 +2734,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2762,10 +2767,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581075</v>
+        <v>581183</v>
       </c>
       <c r="R20" t="n">
-        <v>7053018</v>
+        <v>7052996</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2797,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,12 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124299212</v>
+        <v>124302441</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1139,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581119</v>
+        <v>581183</v>
       </c>
       <c r="R6" t="n">
-        <v>7053034</v>
+        <v>7052996</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124303683</v>
+        <v>124302071</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,39 +1260,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581075</v>
+        <v>581211</v>
       </c>
       <c r="R7" t="n">
-        <v>7053018</v>
+        <v>7053014</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124299905</v>
+        <v>124299212</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,42 +1368,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581157</v>
+        <v>581119</v>
       </c>
       <c r="R8" t="n">
-        <v>7053041</v>
+        <v>7053034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124302024</v>
+        <v>124299626</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91673</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,25 +1480,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581189</v>
+        <v>581134</v>
       </c>
       <c r="R9" t="n">
-        <v>7052999</v>
+        <v>7053050</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,22 +1568,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124303915</v>
+        <v>124300269</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1629,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581062</v>
+        <v>581175</v>
       </c>
       <c r="R10" t="n">
-        <v>7053037</v>
+        <v>7053047</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,22 +1680,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124302493</v>
+        <v>124300324</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581190</v>
+        <v>581191</v>
       </c>
       <c r="R11" t="n">
-        <v>7053006</v>
+        <v>7053034</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,12 +1792,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1930,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124303795</v>
+        <v>124302493</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,25 +1933,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1970,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581080</v>
+        <v>581190</v>
       </c>
       <c r="R13" t="n">
-        <v>7053021</v>
+        <v>7053006</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124302148</v>
+        <v>124303795</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,42 +2045,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581210</v>
+        <v>581080</v>
       </c>
       <c r="R14" t="n">
-        <v>7053013</v>
+        <v>7053021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124302071</v>
+        <v>124298991</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,38 +2157,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581211</v>
+        <v>581099</v>
       </c>
       <c r="R15" t="n">
-        <v>7053014</v>
+        <v>7053032</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,7 +2224,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,7 +2234,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2261,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124300324</v>
+        <v>124299905</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,38 +2273,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581191</v>
+        <v>581157</v>
       </c>
       <c r="R16" t="n">
-        <v>7053034</v>
+        <v>7053041</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2355,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,22 +2365,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124299626</v>
+        <v>124303915</v>
       </c>
       <c r="B17" t="n">
-        <v>91673</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,25 +2389,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581134</v>
+        <v>581062</v>
       </c>
       <c r="R17" t="n">
-        <v>7053050</v>
+        <v>7053037</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2467,7 +2462,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,19 +2477,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124298991</v>
+        <v>124302148</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2529,7 +2524,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2538,10 +2533,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581099</v>
+        <v>581210</v>
       </c>
       <c r="R18" t="n">
-        <v>7053032</v>
+        <v>7053013</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,10 +2605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124300269</v>
+        <v>124303683</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,34 +2621,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581175</v>
+        <v>581075</v>
       </c>
       <c r="R19" t="n">
-        <v>7053047</v>
+        <v>7053018</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,7 +2695,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,22 +2715,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124302441</v>
+        <v>124302024</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,43 +2739,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581183</v>
+        <v>581189</v>
       </c>
       <c r="R20" t="n">
-        <v>7052996</v>
+        <v>7052999</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124302441</v>
+        <v>124302148</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,31 +1139,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581183</v>
+        <v>581210</v>
       </c>
       <c r="R6" t="n">
-        <v>7052996</v>
+        <v>7053013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124302071</v>
+        <v>124303683</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,34 +1259,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581211</v>
+        <v>581075</v>
       </c>
       <c r="R7" t="n">
-        <v>7053014</v>
+        <v>7053018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1333,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124299212</v>
+        <v>124302441</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,38 +1377,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581119</v>
+        <v>581183</v>
       </c>
       <c r="R8" t="n">
-        <v>7053034</v>
+        <v>7052996</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124299626</v>
+        <v>124299212</v>
       </c>
       <c r="B9" t="n">
-        <v>91673</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,25 +1494,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581134</v>
+        <v>581119</v>
       </c>
       <c r="R9" t="n">
-        <v>7053050</v>
+        <v>7053034</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,22 +1582,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124300269</v>
+        <v>124303795</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,21 +1610,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581175</v>
+        <v>581080</v>
       </c>
       <c r="R10" t="n">
-        <v>7053047</v>
+        <v>7053021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,19 +1694,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124300324</v>
+        <v>124303915</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1732,10 +1746,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581191</v>
+        <v>581062</v>
       </c>
       <c r="R11" t="n">
-        <v>7053034</v>
+        <v>7053037</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,22 +1806,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124302611</v>
+        <v>124300324</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,43 +1830,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581184</v>
+        <v>581191</v>
       </c>
       <c r="R12" t="n">
-        <v>7053000</v>
+        <v>7053034</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124302493</v>
+        <v>124302024</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,25 +1942,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581190</v>
+        <v>581189</v>
       </c>
       <c r="R13" t="n">
-        <v>7053006</v>
+        <v>7052999</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124303795</v>
+        <v>124302611</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,38 +2054,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581080</v>
+        <v>581184</v>
       </c>
       <c r="R14" t="n">
-        <v>7053021</v>
+        <v>7053000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,7 +2122,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2132,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,22 +2147,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124298991</v>
+        <v>124302071</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,42 +2171,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581099</v>
+        <v>581211</v>
       </c>
       <c r="R15" t="n">
-        <v>7053032</v>
+        <v>7053014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2234,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124299905</v>
+        <v>124299626</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91673</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,38 +2287,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581157</v>
+        <v>581134</v>
       </c>
       <c r="R16" t="n">
-        <v>7053041</v>
+        <v>7053050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,22 +2371,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124303915</v>
+        <v>124302493</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,25 +2395,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2417,10 +2423,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581062</v>
+        <v>581190</v>
       </c>
       <c r="R17" t="n">
-        <v>7053037</v>
+        <v>7053006</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,7 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124302148</v>
+        <v>124300269</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,42 +2507,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581210</v>
+        <v>581175</v>
       </c>
       <c r="R18" t="n">
-        <v>7053013</v>
+        <v>7053047</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2570,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2578,7 +2580,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,22 +2595,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124303683</v>
+        <v>124298991</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,31 +2619,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2650,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581075</v>
+        <v>581099</v>
       </c>
       <c r="R19" t="n">
-        <v>7053018</v>
+        <v>7053032</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2685,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,12 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,10 +2723,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124302024</v>
+        <v>124299905</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2739,38 +2735,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581189</v>
+        <v>581157</v>
       </c>
       <c r="R20" t="n">
-        <v>7052999</v>
+        <v>7053041</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124302148</v>
+        <v>124299212</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,42 +1139,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581210</v>
+        <v>581119</v>
       </c>
       <c r="R6" t="n">
-        <v>7053013</v>
+        <v>7053034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124302441</v>
+        <v>124300269</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,43 +1373,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581183</v>
+        <v>581175</v>
       </c>
       <c r="R8" t="n">
-        <v>7052996</v>
+        <v>7053047</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124299212</v>
+        <v>124299626</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,25 +1485,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581119</v>
+        <v>581134</v>
       </c>
       <c r="R9" t="n">
-        <v>7053034</v>
+        <v>7053050</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,22 +1573,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124303795</v>
+        <v>124302493</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,25 +1597,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581080</v>
+        <v>581190</v>
       </c>
       <c r="R10" t="n">
-        <v>7053021</v>
+        <v>7053006</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124303915</v>
+        <v>124302071</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,21 +1713,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1746,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581062</v>
+        <v>581211</v>
       </c>
       <c r="R11" t="n">
-        <v>7053037</v>
+        <v>7053014</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124300324</v>
+        <v>124302611</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,38 +1821,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581191</v>
+        <v>581184</v>
       </c>
       <c r="R12" t="n">
-        <v>7053034</v>
+        <v>7053000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124302024</v>
+        <v>124302148</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,38 +1938,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581189</v>
+        <v>581210</v>
       </c>
       <c r="R13" t="n">
-        <v>7052999</v>
+        <v>7053013</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124302611</v>
+        <v>124298991</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,31 +2054,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2087,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581184</v>
+        <v>581099</v>
       </c>
       <c r="R14" t="n">
-        <v>7053000</v>
+        <v>7053032</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2132,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,22 +2146,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124302071</v>
+        <v>124303915</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,21 +2174,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2199,10 +2198,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581211</v>
+        <v>581062</v>
       </c>
       <c r="R15" t="n">
-        <v>7053014</v>
+        <v>7053037</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124299626</v>
+        <v>124299905</v>
       </c>
       <c r="B16" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,34 +2286,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581134</v>
+        <v>581157</v>
       </c>
       <c r="R16" t="n">
-        <v>7053050</v>
+        <v>7053041</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,22 +2374,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124302493</v>
+        <v>124302024</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,25 +2398,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2423,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581190</v>
+        <v>581189</v>
       </c>
       <c r="R17" t="n">
-        <v>7053006</v>
+        <v>7052999</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2468,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124300269</v>
+        <v>124300324</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,21 +2514,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2535,10 +2538,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581175</v>
+        <v>581191</v>
       </c>
       <c r="R18" t="n">
-        <v>7053047</v>
+        <v>7053034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2607,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124298991</v>
+        <v>124302441</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,30 +2622,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2651,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581099</v>
+        <v>581183</v>
       </c>
       <c r="R19" t="n">
-        <v>7053032</v>
+        <v>7052996</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2686,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2723,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124299905</v>
+        <v>124303795</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2735,42 +2739,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581157</v>
+        <v>581080</v>
       </c>
       <c r="R20" t="n">
-        <v>7053041</v>
+        <v>7053021</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124299212</v>
+        <v>124302148</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1139,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581119</v>
+        <v>581210</v>
       </c>
       <c r="R6" t="n">
-        <v>7053034</v>
+        <v>7053013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124303683</v>
+        <v>124303915</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,39 +1259,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581075</v>
+        <v>581062</v>
       </c>
       <c r="R7" t="n">
-        <v>7053018</v>
+        <v>7053037</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124300269</v>
+        <v>124300324</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581175</v>
+        <v>581191</v>
       </c>
       <c r="R8" t="n">
-        <v>7053047</v>
+        <v>7053034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124299626</v>
+        <v>124299212</v>
       </c>
       <c r="B9" t="n">
-        <v>91673</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,25 +1479,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581134</v>
+        <v>581119</v>
       </c>
       <c r="R9" t="n">
-        <v>7053050</v>
+        <v>7053034</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1552,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,22 +1567,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124302493</v>
+        <v>124299905</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,38 +1591,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581190</v>
+        <v>581157</v>
       </c>
       <c r="R10" t="n">
-        <v>7053006</v>
+        <v>7053041</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124302071</v>
+        <v>124302493</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,25 +1707,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581211</v>
+        <v>581190</v>
       </c>
       <c r="R11" t="n">
-        <v>7053014</v>
+        <v>7053006</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124302611</v>
+        <v>124303795</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,43 +1819,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581184</v>
+        <v>581080</v>
       </c>
       <c r="R12" t="n">
-        <v>7053000</v>
+        <v>7053021</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,22 +1907,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124302148</v>
+        <v>124302441</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,30 +1931,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1970,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581210</v>
+        <v>581183</v>
       </c>
       <c r="R13" t="n">
-        <v>7053013</v>
+        <v>7052996</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,7 +1999,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2009,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,10 +2036,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124298991</v>
+        <v>124300269</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,42 +2048,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581099</v>
+        <v>581175</v>
       </c>
       <c r="R14" t="n">
-        <v>7053032</v>
+        <v>7053047</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,19 +2136,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124303915</v>
+        <v>124302024</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2198,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581062</v>
+        <v>581189</v>
       </c>
       <c r="R15" t="n">
-        <v>7053037</v>
+        <v>7052999</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,7 +2223,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,7 +2233,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124299905</v>
+        <v>124302611</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,30 +2272,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581157</v>
+        <v>581184</v>
       </c>
       <c r="R16" t="n">
-        <v>7053041</v>
+        <v>7053000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,22 +2365,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hampus Sangefors</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124302024</v>
+        <v>124298991</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,38 +2389,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581189</v>
+        <v>581099</v>
       </c>
       <c r="R17" t="n">
-        <v>7052999</v>
+        <v>7053032</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124300324</v>
+        <v>124302071</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,21 +2509,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,10 +2533,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581191</v>
+        <v>581211</v>
       </c>
       <c r="R18" t="n">
-        <v>7053034</v>
+        <v>7053014</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,22 +2593,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hampus Sangefors</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124302441</v>
+        <v>124303683</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,31 +2617,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2655,10 +2650,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581183</v>
+        <v>581075</v>
       </c>
       <c r="R19" t="n">
-        <v>7052996</v>
+        <v>7053018</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2695,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124303795</v>
+        <v>124299626</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2739,25 +2739,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581080</v>
+        <v>581134</v>
       </c>
       <c r="R20" t="n">
-        <v>7053021</v>
+        <v>7053050</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,12 +2827,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2837,6 +2837,598 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125455459</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>581126</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7053024</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125455937</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>581238</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7053043</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125456184</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>658</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>581126</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7053024</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125455695</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>581155</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7053024</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125455348</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>581126</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7053024</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -2839,10 +2839,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125455459</v>
+        <v>125456184</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91459</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2851,40 +2851,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+          <t>Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2923,7 +2918,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2933,7 +2928,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2960,10 +2955,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125455937</v>
+        <v>125455459</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2972,31 +2967,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3005,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581238</v>
+        <v>581126</v>
       </c>
       <c r="R22" t="n">
-        <v>7053043</v>
+        <v>7053024</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3040,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3050,12 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,22 +3064,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125456184</v>
+        <v>125455695</v>
       </c>
       <c r="B23" t="n">
-        <v>91299</v>
+        <v>91166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3098,35 +3092,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödmossaloken, Ång</t>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581126</v>
+        <v>581155</v>
       </c>
       <c r="R23" t="n">
         <v>7053024</v>
@@ -3161,7 +3156,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3166,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,10 +3193,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125455695</v>
+        <v>125455937</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3214,27 +3209,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3243,10 +3238,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581155</v>
+        <v>581238</v>
       </c>
       <c r="R24" t="n">
-        <v>7053024</v>
+        <v>7053043</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3278,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3288,7 +3283,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,12 +3303,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
         <v>125455348</v>
       </c>
       <c r="B25" t="n">
-        <v>98122</v>
+        <v>98290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -2839,10 +2839,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125456184</v>
+        <v>125455348</v>
       </c>
       <c r="B21" t="n">
-        <v>91459</v>
+        <v>98290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2851,30 +2851,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2955,10 +2955,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125455459</v>
+        <v>125456184</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
+        <v>91459</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2967,40 +2967,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+          <t>Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -3039,7 +3034,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3044,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3193,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125455937</v>
+        <v>125455459</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3205,31 +3200,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3238,10 +3237,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581238</v>
+        <v>581126</v>
       </c>
       <c r="R24" t="n">
-        <v>7053043</v>
+        <v>7053024</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3273,7 +3272,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,12 +3282,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,22 +3297,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125455348</v>
+        <v>125455937</v>
       </c>
       <c r="B25" t="n">
-        <v>98290</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3327,42 +3321,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödmossaloken, Ång</t>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581126</v>
+        <v>581238</v>
       </c>
       <c r="R25" t="n">
-        <v>7053024</v>
+        <v>7053043</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3389,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,7 +3399,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,12 +3419,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -2839,51 +2839,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125455348</v>
+        <v>125455695</v>
       </c>
       <c r="B21" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödmossaloken, Ång</t>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581126</v>
+        <v>581155</v>
       </c>
       <c r="R21" t="n">
         <v>7053024</v>
@@ -2918,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2928,7 +2924,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2955,15 +2951,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125456184</v>
+        <v>125455937</v>
       </c>
       <c r="B22" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,38 +2962,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rödmossaloken, Ång</t>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581126</v>
+        <v>581238</v>
       </c>
       <c r="R22" t="n">
-        <v>7053024</v>
+        <v>7053043</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3034,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,7 +3036,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,55 +3056,54 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125455695</v>
+        <v>125455459</v>
       </c>
       <c r="B23" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3116,7 +3112,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581155</v>
+        <v>581126</v>
       </c>
       <c r="R23" t="n">
         <v>7053024</v>
@@ -3188,52 +3184,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125455459</v>
+        <v>125456184</v>
       </c>
       <c r="B24" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+          <t>Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3272,7 +3258,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3282,7 +3268,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,55 +3295,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125455937</v>
+        <v>125455348</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+          <t>Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581238</v>
+        <v>581126</v>
       </c>
       <c r="R25" t="n">
-        <v>7053043</v>
+        <v>7053024</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3389,7 +3369,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3399,12 +3379,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,12 +3394,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -2842,7 +2842,7 @@
         <v>125455695</v>
       </c>
       <c r="B21" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>125455459</v>
       </c>
       <c r="B23" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>125456184</v>
       </c>
       <c r="B24" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>125455348</v>
       </c>
       <c r="B25" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -2842,7 +2842,7 @@
         <v>125455695</v>
       </c>
       <c r="B21" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>125455459</v>
       </c>
       <c r="B23" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>125456184</v>
       </c>
       <c r="B24" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>125455348</v>
       </c>
       <c r="B25" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -2842,7 +2842,7 @@
         <v>125455695</v>
       </c>
       <c r="B21" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>125455459</v>
       </c>
       <c r="B23" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>125456184</v>
       </c>
       <c r="B24" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>125455348</v>
       </c>
       <c r="B25" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3071,7 +3071,7 @@
         <v>125455459</v>
       </c>
       <c r="B23" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>125455348</v>
       </c>
       <c r="B25" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -2842,7 +2842,7 @@
         <v>125455695</v>
       </c>
       <c r="B21" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>125455937</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>125455459</v>
       </c>
       <c r="B23" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>125456184</v>
       </c>
       <c r="B24" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>125455348</v>
       </c>
       <c r="B25" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3404,6 +3404,1559 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127276603</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>581146</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7053022</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127276563</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>581147</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7053039</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127277200</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>581116</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7053055</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127276796</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>581177</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7053003</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127277371</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91773</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>581075</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7053048</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127277111</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Rödmossaloken, Rödmossaloken, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>581139</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7053054</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127293651</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91319</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Taråberget m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>581100</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7053055</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127293658</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80143</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Taråberget m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>581190</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7053038</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127293667</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Taråberget m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>581208</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7053009</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127293660</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91615</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>658</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Taråberget m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>581103</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7053036</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127293666</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Taråberget m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>581095</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7053033</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127293652</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91319</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Taråberget m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>581215</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7053019</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127293653</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91319</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Taråberget m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>581107</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7053038</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127293659</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91615</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>658</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Taråberget m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>581108</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7053056</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127293657</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80150</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Taråberget m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>581190</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7053038</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>127276603</v>
       </c>
       <c r="B26" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127276796</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>127277371</v>
       </c>
       <c r="B30" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>127293651</v>
       </c>
       <c r="B32" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>127293658</v>
       </c>
       <c r="B33" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>127293667</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127293660</v>
       </c>
       <c r="B35" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>127293666</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127293652</v>
       </c>
       <c r="B37" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>127293653</v>
       </c>
       <c r="B38" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>127293659</v>
       </c>
       <c r="B39" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127293657</v>
       </c>
       <c r="B40" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>127276603</v>
       </c>
       <c r="B26" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127276796</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>127277371</v>
       </c>
       <c r="B30" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>127293651</v>
       </c>
       <c r="B32" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127293660</v>
       </c>
       <c r="B35" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127293652</v>
       </c>
       <c r="B37" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>127293653</v>
       </c>
       <c r="B38" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>127293659</v>
       </c>
       <c r="B39" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>127276603</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>127276563</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>127277200</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127276796</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>127277371</v>
       </c>
       <c r="B30" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>127277111</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>127293651</v>
       </c>
       <c r="B32" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>127293658</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>127293667</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127293660</v>
       </c>
       <c r="B35" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>127293666</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127293652</v>
       </c>
       <c r="B37" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>127293653</v>
       </c>
       <c r="B38" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>127293659</v>
       </c>
       <c r="B39" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127293657</v>
       </c>
       <c r="B40" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>127276603</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127276796</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3862,45 +3862,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127277371</v>
+        <v>127277111</v>
       </c>
       <c r="B30" t="n">
-        <v>91784</v>
+        <v>57661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581075</v>
+        <v>581139</v>
       </c>
       <c r="R30" t="n">
-        <v>7053048</v>
+        <v>7053054</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,7 +3937,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3942,7 +3947,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,50 +3979,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277111</v>
+        <v>127277371</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>91784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581139</v>
+        <v>581075</v>
       </c>
       <c r="R31" t="n">
-        <v>7053054</v>
+        <v>7053048</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,7 +4049,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4054,12 +4059,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>127276603</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>127276563</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>127277200</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127276796</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3862,50 +3862,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127277111</v>
+        <v>127277371</v>
       </c>
       <c r="B30" t="n">
-        <v>57661</v>
+        <v>91786</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581139</v>
+        <v>581075</v>
       </c>
       <c r="R30" t="n">
-        <v>7053054</v>
+        <v>7053048</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3937,7 +3932,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3947,12 +3942,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3979,45 +3969,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277371</v>
+        <v>127277111</v>
       </c>
       <c r="B31" t="n">
-        <v>91784</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581075</v>
+        <v>581139</v>
       </c>
       <c r="R31" t="n">
-        <v>7053048</v>
+        <v>7053054</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4049,7 +4044,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4059,7 +4054,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4089,7 +4089,7 @@
         <v>127293651</v>
       </c>
       <c r="B32" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>127293658</v>
       </c>
       <c r="B33" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>127293667</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127293660</v>
       </c>
       <c r="B35" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>127293666</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127293652</v>
       </c>
       <c r="B37" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>127293653</v>
       </c>
       <c r="B38" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>127293659</v>
       </c>
       <c r="B39" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127293657</v>
       </c>
       <c r="B40" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3862,45 +3862,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127277371</v>
+        <v>127277111</v>
       </c>
       <c r="B30" t="n">
-        <v>91786</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581075</v>
+        <v>581139</v>
       </c>
       <c r="R30" t="n">
-        <v>7053048</v>
+        <v>7053054</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,7 +3937,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3942,7 +3947,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,50 +3979,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277111</v>
+        <v>127277371</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>91786</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581139</v>
+        <v>581075</v>
       </c>
       <c r="R31" t="n">
-        <v>7053054</v>
+        <v>7053048</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,7 +4049,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4054,12 +4059,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3862,50 +3862,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127277111</v>
+        <v>127277371</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>91786</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581139</v>
+        <v>581075</v>
       </c>
       <c r="R30" t="n">
-        <v>7053054</v>
+        <v>7053048</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3937,7 +3932,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3947,12 +3942,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3979,45 +3969,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277371</v>
+        <v>127277111</v>
       </c>
       <c r="B31" t="n">
-        <v>91786</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581075</v>
+        <v>581139</v>
       </c>
       <c r="R31" t="n">
-        <v>7053048</v>
+        <v>7053054</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4049,7 +4044,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4059,7 +4054,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>127276603</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127276796</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>127277371</v>
       </c>
       <c r="B30" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>127293651</v>
       </c>
       <c r="B32" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127293660</v>
       </c>
       <c r="B35" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127293652</v>
       </c>
       <c r="B37" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>127293653</v>
       </c>
       <c r="B38" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>127293659</v>
       </c>
       <c r="B39" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>127276603</v>
       </c>
       <c r="B26" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>127276563</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>127277200</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127276796</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>127277371</v>
       </c>
       <c r="B30" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>127277111</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>127293651</v>
       </c>
       <c r="B32" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>127293658</v>
       </c>
       <c r="B33" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>127293667</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127293660</v>
       </c>
       <c r="B35" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>127293666</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127293652</v>
       </c>
       <c r="B37" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>127293653</v>
       </c>
       <c r="B38" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>127293659</v>
       </c>
       <c r="B39" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127293657</v>
       </c>
       <c r="B40" t="n">
-        <v>80159</v>
+        <v>80162</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>127276603</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>127276563</v>
       </c>
       <c r="B27" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>127277200</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127276796</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3862,45 +3862,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127277371</v>
+        <v>127277111</v>
       </c>
       <c r="B30" t="n">
-        <v>91795</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581075</v>
+        <v>581139</v>
       </c>
       <c r="R30" t="n">
-        <v>7053048</v>
+        <v>7053054</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,7 +3937,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3942,7 +3947,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,50 +3979,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127277111</v>
+        <v>127277371</v>
       </c>
       <c r="B31" t="n">
-        <v>57666</v>
+        <v>91803</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rödmossaloken, Rödmossaloken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581139</v>
+        <v>581075</v>
       </c>
       <c r="R31" t="n">
-        <v>7053054</v>
+        <v>7053048</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,7 +4049,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4054,12 +4059,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4089,7 +4089,7 @@
         <v>127293651</v>
       </c>
       <c r="B32" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>127293658</v>
       </c>
       <c r="B33" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>127293667</v>
       </c>
       <c r="B34" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127293660</v>
       </c>
       <c r="B35" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>127293666</v>
       </c>
       <c r="B36" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127293652</v>
       </c>
       <c r="B37" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>127293653</v>
       </c>
       <c r="B38" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>127293659</v>
       </c>
       <c r="B39" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127293657</v>
       </c>
       <c r="B40" t="n">
-        <v>80162</v>
+        <v>80168</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51064-2024 artfynd.xlsx
+++ b/artfynd/A 51064-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>127276603</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127276796</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>127277371</v>
       </c>
       <c r="B31" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>127293651</v>
       </c>
       <c r="B32" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127293660</v>
       </c>
       <c r="B35" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127293652</v>
       </c>
       <c r="B37" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>127293653</v>
       </c>
       <c r="B38" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>127293659</v>
       </c>
       <c r="B39" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
